--- a/data/trans_orig/P0801-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2007</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>761881</t>
+          <t>760252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>813417</t>
+          <t>815291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>732209</t>
+          <t>734220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>803210</t>
+          <t>804239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1508332</t>
+          <t>1510289</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1600200</t>
+          <t>1602484</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>148362</t>
+          <t>149654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>193589</t>
+          <t>194404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>367491</t>
+          <t>365123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>432599</t>
+          <t>430593</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531620</t>
+          <t>526065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>613142</t>
+          <t>608485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57874</t>
+          <t>57099</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89544</t>
+          <t>88304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>126242</t>
+          <t>125784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>171201</t>
+          <t>170942</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>192679</t>
+          <t>194477</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247364</t>
+          <t>249928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1577161</t>
+          <t>1577911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1615609</t>
+          <t>1616583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1429097</t>
+          <t>1432088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1472666</t>
+          <t>1474575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3021478</t>
+          <t>3024385</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3078606</t>
+          <t>3081187</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58558</t>
+          <t>57639</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93498</t>
+          <t>92927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,47 +1317,47 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>106922</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>87682</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>126589</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>106922</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>89977</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>128856</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>156304</t>
+          <t>155122</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>209189</t>
+          <t>207276</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12914</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18586</t>
+          <t>18137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39728</t>
+          <t>39015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37190</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64188</t>
+          <t>64482</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>511956</t>
+          <t>512160</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>532668</t>
+          <t>533981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>418639</t>
+          <t>418075</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>445833</t>
+          <t>444030</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>939675</t>
+          <t>938525</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>973171</t>
+          <t>973920</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,76%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28408</t>
+          <t>30212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>25013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49018</t>
+          <t>48706</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68445</t>
+          <t>70786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16777</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2876172</t>
+          <t>2876209</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2943079</t>
+          <t>2946110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2603467</t>
+          <t>2605295</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2703467</t>
+          <t>2701280</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5500015</t>
+          <t>5510525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5624881</t>
+          <t>5624915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>235373</t>
+          <t>233979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294119</t>
+          <t>294603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>499517</t>
+          <t>501078</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>582911</t>
+          <t>587800</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>751247</t>
+          <t>751730</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>859559</t>
+          <t>855295</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83807</t>
+          <t>84180</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120021</t>
+          <t>124806</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>158379</t>
+          <t>156249</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>211446</t>
+          <t>209051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>250157</t>
+          <t>252141</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>316877</t>
+          <t>317893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2012</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>633989</t>
+          <t>632603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>696639</t>
+          <t>693951</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>653372</t>
+          <t>650114</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>725743</t>
+          <t>724256</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1309070</t>
+          <t>1297498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1405429</t>
+          <t>1396838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,41%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163070</t>
+          <t>163581</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>213655</t>
+          <t>214642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>363578</t>
+          <t>360734</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433203</t>
+          <t>430361</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>538284</t>
+          <t>541992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>620545</t>
+          <t>624896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99760</t>
+          <t>102927</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>146995</t>
+          <t>148348</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>225948</t>
+          <t>227053</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>288301</t>
+          <t>288385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>342396</t>
+          <t>342543</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>417302</t>
+          <t>415833</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1775617</t>
+          <t>1781757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1829782</t>
+          <t>1832158</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1516004</t>
+          <t>1519568</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1577170</t>
+          <t>1575265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3311822</t>
+          <t>3312076</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3392539</t>
+          <t>3392035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100430</t>
+          <t>97898</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>146706</t>
+          <t>142482</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>129465</t>
+          <t>126421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181852</t>
+          <t>176750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>240741</t>
+          <t>236951</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>305393</t>
+          <t>305920</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27458</t>
+          <t>26481</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52350</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>43015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77463</t>
+          <t>76505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78549</t>
+          <t>74944</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>122349</t>
+          <t>118515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431134</t>
+          <t>431919</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>457653</t>
+          <t>458292</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>404265</t>
+          <t>404039</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>430231</t>
+          <t>429891</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>844799</t>
+          <t>844056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>881524</t>
+          <t>880723</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>18272</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40968</t>
+          <t>41777</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>48378</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47279</t>
+          <t>46699</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80426</t>
+          <t>78905</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2791</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2915</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>14027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23714</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2875890</t>
+          <t>2876251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2962045</t>
+          <t>2957425</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2603490</t>
+          <t>2601971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2712299</t>
+          <t>2710460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5505143</t>
+          <t>5511148</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5636901</t>
+          <t>5644927</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,94%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>297651</t>
+          <t>301063</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370819</t>
+          <t>370374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537367</t>
+          <t>537288</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>623031</t>
+          <t>622095</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>862765</t>
+          <t>855288</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>974782</t>
+          <t>970673</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>143119</t>
+          <t>140126</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198984</t>
+          <t>194107</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>284742</t>
+          <t>284970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>352691</t>
+          <t>356655</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>444252</t>
+          <t>444988</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>530406</t>
+          <t>534712</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2016</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>483682</t>
+          <t>476301</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>531286</t>
+          <t>530184</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>489875</t>
+          <t>486693</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>553609</t>
+          <t>555226</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>989135</t>
+          <t>985931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1071853</t>
+          <t>1072101</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,3%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143719</t>
+          <t>141908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187408</t>
+          <t>187861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246465</t>
+          <t>245385</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305391</t>
+          <t>307756</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>404170</t>
+          <t>402609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>481000</t>
+          <t>479331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65870</t>
+          <t>66460</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99577</t>
+          <t>99415</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>172344</t>
+          <t>171612</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>227325</t>
+          <t>227612</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251365</t>
+          <t>252141</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>316295</t>
+          <t>314221</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1866128</t>
+          <t>1864075</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1915736</t>
+          <t>1916102</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1674192</t>
+          <t>1675893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739540</t>
+          <t>1739156</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3556258</t>
+          <t>3556600</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3640529</t>
+          <t>3637031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111146</t>
+          <t>109209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>154385</t>
+          <t>156029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>169983</t>
+          <t>172300</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>228369</t>
+          <t>227677</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>293781</t>
+          <t>295718</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>367062</t>
+          <t>367054</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>40338</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68740</t>
+          <t>69848</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64314</t>
+          <t>62878</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100088</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111332</t>
+          <t>114251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158559</t>
+          <t>160824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>495390</t>
+          <t>492697</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>520674</t>
+          <t>519286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>487355</t>
+          <t>488000</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>515657</t>
+          <t>515639</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>990623</t>
+          <t>992992</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1029514</t>
+          <t>1030030</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39950</t>
+          <t>40582</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39056</t>
+          <t>39097</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40790</t>
+          <t>39092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73129</t>
+          <t>70313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>20339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10703</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>30777</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>43887</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2866132</t>
+          <t>2865345</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2952201</t>
+          <t>2945573</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2681633</t>
+          <t>2678812</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2783703</t>
+          <t>2784973</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5570652</t>
+          <t>5575605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5706047</t>
+          <t>5706641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,59%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>287969</t>
+          <t>291142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>358741</t>
+          <t>361022</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460492</t>
+          <t>457517</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>547132</t>
+          <t>542714</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>768781</t>
+          <t>772551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>882977</t>
+          <t>879837</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125718</t>
+          <t>123450</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>172918</t>
+          <t>170791</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>263876</t>
+          <t>265333</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>333176</t>
+          <t>337450</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>400559</t>
+          <t>405986</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>489748</t>
+          <t>487239</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según limitación a hacer esfuerzos moderados en 2023</t>
+          <t>Población según limitación a hacer esfuerzos moderados en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>321623</t>
+          <t>321675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>362921</t>
+          <t>361981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>330821</t>
+          <t>329362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>373324</t>
+          <t>375672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>668951</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>726858</t>
+          <t>724412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,65%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,02%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87495</t>
+          <t>87540</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120275</t>
+          <t>120167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203873</t>
+          <t>203392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242297</t>
+          <t>243758</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>298984</t>
+          <t>301338</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>349451</t>
+          <t>351664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57475</t>
+          <t>56473</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83536</t>
+          <t>82462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166290</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>199718</t>
+          <t>199482</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>229230</t>
+          <t>228266</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>272550</t>
+          <t>272497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,7 +7209,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1238941</t>
+          <t>1205677</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2011200</t>
+          <t>2012499</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1900026</t>
+          <t>1899690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2019607</t>
+          <t>2024358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3119322</t>
+          <t>3010762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3963146</t>
+          <t>3963334</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>212719</t>
+          <t>213996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1014957</t>
+          <t>1051058</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164989</t>
+          <t>165957</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255954</t>
+          <t>260401</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>429554</t>
+          <t>430240</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1291864</t>
+          <t>1407058</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>31,07%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40808</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77867</t>
+          <t>78639</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52304</t>
+          <t>51490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88308</t>
+          <t>86554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>102389</t>
+          <t>101340</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>156393</t>
+          <t>157120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>594012</t>
+          <t>592666</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>616261</t>
+          <t>615255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>591672</t>
+          <t>592778</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>613909</t>
+          <t>614853</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1193634</t>
+          <t>1194458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1225054</t>
+          <t>1224662</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19670</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35320</t>
+          <t>34734</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54758</t>
+          <t>54645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>60215</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86826</t>
+          <t>85828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>19531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20186</t>
+          <t>19942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35092</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2130115</t>
+          <t>2157023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2956275</t>
+          <t>2960062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2832730</t>
+          <t>2833486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3061196</t>
+          <t>3034917</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4932229</t>
+          <t>4947266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5870576</t>
+          <t>5877940</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>346111</t>
+          <t>345396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1205428</t>
+          <t>1192820</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>397577</t>
+          <t>404876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>537137</t>
+          <t>534867</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>821986</t>
+          <t>820907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1818960</t>
+          <t>1840798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,91%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107062</t>
+          <t>110002</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167492</t>
+          <t>164143</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>219356</t>
+          <t>216612</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>297408</t>
+          <t>297687</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>353728</t>
+          <t>351710</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>452490</t>
+          <t>451438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P0801-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P0801-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>760252</t>
+          <t>759471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>815291</t>
+          <t>812229</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>734220</t>
+          <t>735739</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>804239</t>
+          <t>805424</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1510289</t>
+          <t>1508859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1602484</t>
+          <t>1597478</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149654</t>
+          <t>149209</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>194404</t>
+          <t>195558</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>365123</t>
+          <t>366206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430593</t>
+          <t>431768</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>526065</t>
+          <t>533554</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>608485</t>
+          <t>610214</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,0%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57099</t>
+          <t>56467</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88304</t>
+          <t>89340</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125784</t>
+          <t>125351</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>170942</t>
+          <t>171102</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>194477</t>
+          <t>193570</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>249928</t>
+          <t>249648</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1577911</t>
+          <t>1576361</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1616583</t>
+          <t>1615365</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1432088</t>
+          <t>1430236</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1474575</t>
+          <t>1474732</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3024385</t>
+          <t>3021608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3081187</t>
+          <t>3079098</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57639</t>
+          <t>59317</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>92927</t>
+          <t>93064</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87682</t>
+          <t>89161</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126589</t>
+          <t>128822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,47 +1352,47 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>181028</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>158634</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>208567</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
           <t>5,52%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>181028</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>155122</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>207276</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>39315</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64482</t>
+          <t>65152</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>512160</t>
+          <t>512599</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533981</t>
+          <t>534358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>418075</t>
+          <t>417186</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>444030</t>
+          <t>444184</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>938525</t>
+          <t>939460</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>973920</t>
+          <t>972384</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30212</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25013</t>
+          <t>23890</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48706</t>
+          <t>48432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>41368</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70786</t>
+          <t>70463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>17281</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3802</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27089</t>
+          <t>27064</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2876209</t>
+          <t>2873378</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2946110</t>
+          <t>2944631</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2605295</t>
+          <t>2600192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2701280</t>
+          <t>2696356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5510525</t>
+          <t>5501381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5624915</t>
+          <t>5625201</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>233979</t>
+          <t>234104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294603</t>
+          <t>296807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>501078</t>
+          <t>504133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>587800</t>
+          <t>590426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>751730</t>
+          <t>754279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>855295</t>
+          <t>859064</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84180</t>
+          <t>84760</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124806</t>
+          <t>124309</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156249</t>
+          <t>157790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>209051</t>
+          <t>210321</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>252141</t>
+          <t>251566</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>317893</t>
+          <t>317654</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>632603</t>
+          <t>634014</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>693951</t>
+          <t>695158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>650114</t>
+          <t>648793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>724256</t>
+          <t>722972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1297498</t>
+          <t>1302454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1396838</t>
+          <t>1401995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,63%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163581</t>
+          <t>162994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>214642</t>
+          <t>212271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>360734</t>
+          <t>361217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430361</t>
+          <t>427960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>541992</t>
+          <t>540263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>624896</t>
+          <t>622330</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>102927</t>
+          <t>101665</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148348</t>
+          <t>147191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>227053</t>
+          <t>229701</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>288385</t>
+          <t>282460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>342543</t>
+          <t>340435</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>415833</t>
+          <t>413709</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1781757</t>
+          <t>1781040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1832158</t>
+          <t>1830743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1519568</t>
+          <t>1516700</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1575265</t>
+          <t>1573967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3312076</t>
+          <t>3310079</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3392035</t>
+          <t>3389839</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97898</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>142482</t>
+          <t>144362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126421</t>
+          <t>129916</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>176750</t>
+          <t>176862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>236951</t>
+          <t>239869</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>305920</t>
+          <t>304846</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26481</t>
+          <t>25750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52795</t>
+          <t>50951</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>43970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>77746</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74944</t>
+          <t>78336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118515</t>
+          <t>120328</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431919</t>
+          <t>429415</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>458292</t>
+          <t>456517</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>404039</t>
+          <t>406040</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>429891</t>
+          <t>431707</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>844056</t>
+          <t>844283</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>880723</t>
+          <t>881866</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18272</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41777</t>
+          <t>41587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3833,7 +3833,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23558</t>
+          <t>22231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48378</t>
+          <t>45048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46699</t>
+          <t>46310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78905</t>
+          <t>80834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15488</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7252</t>
+          <t>7078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22343</t>
+          <t>23222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2876251</t>
+          <t>2873233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2957425</t>
+          <t>2964484</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2601971</t>
+          <t>2602764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2710460</t>
+          <t>2706079</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5511148</t>
+          <t>5508276</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5644927</t>
+          <t>5643433</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,02%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,92%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>301063</t>
+          <t>299131</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>370374</t>
+          <t>373612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>537288</t>
+          <t>533025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622095</t>
+          <t>620896</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>855288</t>
+          <t>855550</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>970673</t>
+          <t>974201</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140126</t>
+          <t>141616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>194107</t>
+          <t>193243</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>284970</t>
+          <t>286216</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>356655</t>
+          <t>356105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>444988</t>
+          <t>440707</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>534712</t>
+          <t>531259</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>476301</t>
+          <t>480534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>530184</t>
+          <t>531211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>486693</t>
+          <t>488996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>555226</t>
+          <t>554042</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>985931</t>
+          <t>989100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1072101</t>
+          <t>1069497</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>141908</t>
+          <t>145953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187861</t>
+          <t>191411</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245385</t>
+          <t>245704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>307756</t>
+          <t>306051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>402609</t>
+          <t>404050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>479331</t>
+          <t>476542</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66460</t>
+          <t>67024</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99415</t>
+          <t>99803</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>171612</t>
+          <t>173698</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>227612</t>
+          <t>226181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>252141</t>
+          <t>249591</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>314221</t>
+          <t>313660</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1864075</t>
+          <t>1863723</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1916102</t>
+          <t>1917454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1675893</t>
+          <t>1674819</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739156</t>
+          <t>1742150</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3556600</t>
+          <t>3557139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3637031</t>
+          <t>3641367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>109209</t>
+          <t>109185</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>156029</t>
+          <t>156805</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>172300</t>
+          <t>170538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>227677</t>
+          <t>230602</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>295718</t>
+          <t>297892</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>367054</t>
+          <t>365254</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40338</t>
+          <t>39173</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69848</t>
+          <t>69685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62878</t>
+          <t>63328</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100550</t>
+          <t>100280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114251</t>
+          <t>110536</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160824</t>
+          <t>157558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>492697</t>
+          <t>494928</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>519286</t>
+          <t>521496</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>488000</t>
+          <t>486861</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>515639</t>
+          <t>516322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>992992</t>
+          <t>993495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1030030</t>
+          <t>1030278</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>17147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40582</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39097</t>
+          <t>40847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70313</t>
+          <t>69836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20339</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30777</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43887</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2865345</t>
+          <t>2867887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2945573</t>
+          <t>2946515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2678812</t>
+          <t>2674974</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2784973</t>
+          <t>2784800</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5575605</t>
+          <t>5571417</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5706641</t>
+          <t>5703271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>291142</t>
+          <t>293364</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>361022</t>
+          <t>361253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>457517</t>
+          <t>457632</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>542714</t>
+          <t>550327</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>772551</t>
+          <t>776030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>879837</t>
+          <t>879679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,7 +6409,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>123450</t>
+          <t>125288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170791</t>
+          <t>171291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>265333</t>
+          <t>265074</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>337450</t>
+          <t>333759</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>405986</t>
+          <t>400355</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>487239</t>
+          <t>481994</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>343479</t>
+          <t>395079</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>321675</t>
+          <t>372173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>361981</t>
+          <t>414487</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>351929</t>
+          <t>387077</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>329362</t>
+          <t>366079</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>375672</t>
+          <t>410078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>695408</t>
+          <t>782156</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>752753</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>724412</t>
+          <t>815382</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>58,22%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>102302</t>
+          <t>109422</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87540</t>
+          <t>92745</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120167</t>
+          <t>127445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>222028</t>
+          <t>234850</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>203392</t>
+          <t>214553</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243758</t>
+          <t>255749</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>324330</t>
+          <t>344272</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>301338</t>
+          <t>317138</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>351664</t>
+          <t>371267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69157</t>
+          <t>74027</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56473</t>
+          <t>60576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>82462</t>
+          <t>89056</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>181551</t>
+          <t>200111</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165441</t>
+          <t>180770</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>199482</t>
+          <t>220056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>250707</t>
+          <t>274139</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>228266</t>
+          <t>252783</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>272497</t>
+          <t>297976</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1786872</t>
+          <t>1950295</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1205677</t>
+          <t>1917323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2012499</t>
+          <t>1979712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1944311</t>
+          <t>1843049</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1899690</t>
+          <t>1816343</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2024358</t>
+          <t>1869253</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3731183</t>
+          <t>3793345</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3010762</t>
+          <t>3750820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3963334</t>
+          <t>3835048</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>443643</t>
+          <t>213894</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>213996</t>
+          <t>188610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1051058</t>
+          <t>246127</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>222152</t>
+          <t>246527</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165957</t>
+          <t>223466</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260401</t>
+          <t>269127</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>665795</t>
+          <t>460421</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>430240</t>
+          <t>425222</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1407058</t>
+          <t>500358</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>59812</t>
+          <t>66377</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41078</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>78639</t>
+          <t>83823</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,67 +7610,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>71360</t>
+          <t>81816</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>68618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86554</t>
+          <t>96978</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>148192</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>126371</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>170423</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>131172</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>101340</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>157120</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>605432</t>
+          <t>665686</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>592666</t>
+          <t>651845</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>615255</t>
+          <t>677585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>604253</t>
+          <t>668685</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592778</t>
+          <t>654523</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>614853</t>
+          <t>680399</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1209685</t>
+          <t>1334371</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1194458</t>
+          <t>1315950</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1224662</t>
+          <t>1350414</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,36%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28848</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>21936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39776</t>
+          <t>41988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,32 +7953,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>49981</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34734</t>
+          <t>40997</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54645</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>81123</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60215</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85828</t>
+          <t>97480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19531</t>
+          <t>23718</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12590</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7763</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19942</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24934</t>
+          <t>30970</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>22496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>42132</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2735784</t>
+          <t>3011062</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2157023</t>
+          <t>2965743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2960062</t>
+          <t>3052196</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2900493</t>
+          <t>2898811</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2833486</t>
+          <t>2855044</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3034917</t>
+          <t>2936936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5636277</t>
+          <t>5909873</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4947266</t>
+          <t>5851027</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5877940</t>
+          <t>5970796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>574793</t>
+          <t>354458</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>345396</t>
+          <t>316276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1192820</t>
+          <t>392539</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>487800</t>
+          <t>531358</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>404876</t>
+          <t>500614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>534867</t>
+          <t>565210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1062592</t>
+          <t>885816</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>820907</t>
+          <t>833974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1840798</t>
+          <t>936258</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>141313</t>
+          <t>155163</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110002</t>
+          <t>132411</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164143</t>
+          <t>178953</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>265501</t>
+          <t>298138</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>216612</t>
+          <t>273210</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>297687</t>
+          <t>326569</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>406814</t>
+          <t>453301</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>351710</t>
+          <t>416360</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>451438</t>
+          <t>488909</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
